--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,58</t>
+          <t>2,08; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,49</t>
+          <t>2,55; 4,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,05</t>
+          <t>2,63; 4,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,5</t>
+          <t>0,7; 2,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,65</t>
+          <t>1,96; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,76</t>
+          <t>1,28; 2,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,25</t>
+          <t>0,67; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,86</t>
+          <t>0,5; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,81</t>
+          <t>0,69; 1,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,06</t>
+          <t>0,76; 2,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,67</t>
+          <t>1,35; 2,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,07</t>
+          <t>1,19; 2,11</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,18</t>
+          <t>1,24; 2,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,64</t>
+          <t>1,82; 2,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,3</t>
+          <t>1,65; 2,26</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13219; 29055</t>
+          <t>13185; 28375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19146; 32586</t>
+          <t>18468; 32182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34668; 55043</t>
+          <t>35831; 55863</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7283; 29841</t>
+          <t>8318; 28359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18882; 34983</t>
+          <t>18826; 34290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29304; 59381</t>
+          <t>27551; 55928</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4878; 15854</t>
+          <t>4733; 15781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4736; 17333</t>
+          <t>4648; 17377</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11922; 29617</t>
+          <t>11354; 29913</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7080; 19053</t>
+          <t>6999; 18597</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14708; 29172</t>
+          <t>14759; 29340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24671; 41898</t>
+          <t>24040; 42587</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43611; 75307</t>
+          <t>42948; 74293</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67168; 97876</t>
+          <t>67461; 98508</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119339; 164653</t>
+          <t>118415; 162345</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,47</t>
+          <t>1,99; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,44</t>
+          <t>2,79; 4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,11</t>
+          <t>2,61; 4,14</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,38</t>
+          <t>1,07; 3,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,58</t>
+          <t>1,89; 3,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,6</t>
+          <t>1,65; 2,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,24</t>
+          <t>0,69; 2,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,86</t>
+          <t>0,85; 2,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,83</t>
+          <t>0,93; 1,87</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,01</t>
+          <t>0,76; 1,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,68</t>
+          <t>1,46; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,11</t>
+          <t>1,27; 2,23</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,15</t>
+          <t>1,4; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,65</t>
+          <t>2,05; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,26</t>
+          <t>1,8; 2,34</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>47030</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13185; 28375</t>
+          <t>13727; 30269</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18468; 32182</t>
+          <t>20503; 33491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35831; 55863</t>
+          <t>37182; 59036</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42722</t>
+          <t>45732</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8318; 28359</t>
+          <t>11213; 33987</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18826; 34290</t>
+          <t>20231; 36788</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27551; 55928</t>
+          <t>34976; 61412</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>22174</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4733; 15781</t>
+          <t>5533; 17511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4648; 17377</t>
+          <t>6890; 17989</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11354; 29913</t>
+          <t>15065; 30286</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>35432</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6999; 18597</t>
+          <t>7523; 19568</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14759; 29340</t>
+          <t>16354; 30925</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24040; 42587</t>
+          <t>26775; 47045</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42948; 74293</t>
+          <t>49532; 79977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67461; 98508</t>
+          <t>76532; 104053</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118415; 162345</t>
+          <t>130647; 170365</t>
         </is>
       </c>
     </row>
